--- a/data/trans_orig/TAM_HOG-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/TAM_HOG-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de personas que viven habitualmente en el hogar</t>
+          <t>Número medio de personas que viven habitualmente en el hogar (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,17 +716,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 3,34</t>
+          <t>3,16; 3,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,03; 3,23</t>
+          <t>3,04; 3,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,86; 3,06</t>
+          <t>2,85; 3,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,07; 3,22</t>
+          <t>3,07; 3,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,51; 2,65</t>
+          <t>2,51; 2,64</t>
         </is>
       </c>
     </row>
@@ -856,27 +856,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 3,39</t>
+          <t>3,23; 3,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 3,37</t>
+          <t>3,2; 3,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 3,16</t>
+          <t>2,98; 3,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 3,52</t>
+          <t>2,83; 3,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,25; 3,44</t>
+          <t>3,26; 3,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -886,22 +886,22 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 3,16</t>
+          <t>2,99; 3,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 2,91</t>
+          <t>2,78; 2,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,27; 3,39</t>
+          <t>3,27; 3,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,25; 3,36</t>
+          <t>3,24; 3,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,95; 3,13</t>
+          <t>2,95; 3,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 3,26</t>
+          <t>3,05; 3,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 2,89</t>
+          <t>2,69; 2,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 3,26</t>
+          <t>3,06; 3,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,22 +1031,22 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,9; 3,12</t>
+          <t>2,89; 3,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 3,16</t>
+          <t>3,02; 3,15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,1; 3,23</t>
+          <t>3,09; 3,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,85; 2,99</t>
+          <t>2,86; 2,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1136,27 +1136,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,98; 3,14</t>
+          <t>2,97; 3,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,0; 3,16</t>
+          <t>2,99; 3,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 2,89</t>
+          <t>2,73; 2,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,61; 2,79</t>
+          <t>2,6; 2,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,05; 3,21</t>
+          <t>3,04; 3,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1166,12 +1166,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,66; 2,81</t>
+          <t>2,65; 2,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,5; 2,72</t>
+          <t>2,51; 2,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,98; 3,09</t>
+          <t>2,98; 3,1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,71; 2,83</t>
+          <t>2,71; 2,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,12; 3,21</t>
+          <t>3,12; 3,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1286,17 +1286,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,89; 2,98</t>
+          <t>2,89; 2,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 3,09</t>
+          <t>2,7; 3,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,17; 3,27</t>
+          <t>3,17; 3,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,73; 2,84</t>
+          <t>2,72; 2,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,74; 2,94</t>
+          <t>2,74; 2,92</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/TAM_HOG-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/TAM_HOG-Habitat-trans_orig.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,66</t>
+          <t>2,65</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -716,12 +716,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 3,33</t>
+          <t>3,15; 3,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 3,23</t>
+          <t>3,04; 3,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,27 +731,27 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,37; 2,57</t>
+          <t>2,38; 2,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,15; 3,35</t>
+          <t>3,17; 3,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,06; 3,27</t>
+          <t>3,05; 3,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 3,07</t>
+          <t>2,88; 3,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 2,75</t>
+          <t>2,57; 2,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,51; 2,64</t>
+          <t>2,5; 2,63</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,1</t>
+          <t>2,85</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,84</t>
+          <t>2,88</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,98</t>
+          <t>2,87</t>
         </is>
       </c>
     </row>
@@ -856,27 +856,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 3,4</t>
+          <t>3,22; 3,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,2; 3,37</t>
+          <t>3,21; 3,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,98; 3,16</t>
+          <t>2,99; 3,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 3,57</t>
+          <t>2,77; 2,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 3,45</t>
+          <t>3,26; 3,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -886,17 +886,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 3,15</t>
+          <t>3,0; 3,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 2,92</t>
+          <t>2,81; 2,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,27; 3,4</t>
+          <t>3,26; 3,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,01; 3,13</t>
+          <t>3,02; 3,13</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 3,33</t>
+          <t>2,8; 2,92</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,77</t>
+          <t>2,78</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,98</t>
+          <t>2,96</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,89</t>
+          <t>2,87</t>
         </is>
       </c>
     </row>
@@ -996,22 +996,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,95; 3,14</t>
+          <t>2,94; 3,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,05; 3,25</t>
+          <t>3,05; 3,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 3,02</t>
+          <t>2,83; 3,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 2,88</t>
+          <t>2,67; 2,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 3,25</t>
+          <t>3,06; 3,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 3,02</t>
+          <t>2,82; 3,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 3,11</t>
+          <t>2,88; 3,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1041,17 +1041,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,09; 3,23</t>
+          <t>3,1; 3,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,86; 2,99</t>
+          <t>2,85; 2,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 2,98</t>
+          <t>2,8; 2,95</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,69</t>
+          <t>2,72</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,64</t>
+          <t>2,7</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,67</t>
+          <t>2,71</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 2,89</t>
+          <t>2,72; 2,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 2,79</t>
+          <t>2,62; 2,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1161,22 +1161,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 3,08</t>
+          <t>2,92; 3,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 2,81</t>
+          <t>2,65; 2,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 2,72</t>
+          <t>2,63; 2,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,04; 3,15</t>
+          <t>3,03; 3,16</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 2,73</t>
+          <t>2,65; 2,77</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,81</t>
+          <t>2,72</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,78</t>
+          <t>2,8</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,79</t>
+          <t>2,76</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,12; 3,2</t>
+          <t>3,12; 3,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,89; 2,99</t>
+          <t>2,9; 2,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 3,08</t>
+          <t>2,67; 2,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,72; 2,83</t>
+          <t>2,76; 2,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,16; 3,22</t>
+          <t>3,16; 3,23</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,9; 2,96</t>
+          <t>2,9; 2,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,74; 2,92</t>
+          <t>2,73; 2,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/TAM_HOG-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/TAM_HOG-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de personas que viven habitualmente en el hogar (tasa de respuesta: 100,0%)</t>
+          <t>Número medio de personas que conviven habitualmente en la vivienda (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
